--- a/Team-Data/2011-12/4-16-2011-12.xlsx
+++ b/Team-Data/2011-12/4-16-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>25</v>
       </c>
       <c r="G2" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="H2" t="n">
         <v>49.1</v>
@@ -679,7 +746,7 @@
         <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K2" t="n">
         <v>0.449</v>
@@ -688,31 +755,31 @@
         <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.363</v>
+        <v>0.365</v>
       </c>
       <c r="O2" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P2" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R2" t="n">
         <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T2" t="n">
         <v>41.2</v>
       </c>
       <c r="U2" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V2" t="n">
         <v>13.9</v>
@@ -721,34 +788,34 @@
         <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y2" t="n">
         <v>4.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF2" t="n">
         <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -769,16 +836,16 @@
         <v>13</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
@@ -790,10 +857,10 @@
         <v>23</v>
       </c>
       <c r="AU2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
@@ -814,7 +881,7 @@
         <v>18</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>2.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
@@ -933,16 +1000,16 @@
         <v>8</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -954,7 +1021,7 @@
         <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>28</v>
@@ -966,19 +1033,19 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
         <v>18</v>
       </c>
       <c r="AW3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
         <v>6</v>
@@ -996,7 +1063,7 @@
         <v>26</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -1025,58 +1092,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>0.117</v>
+        <v>0.119</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.5</v>
+        <v>33.7</v>
       </c>
       <c r="J4" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.416</v>
+        <v>0.418</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
         <v>13.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.298</v>
+        <v>0.303</v>
       </c>
       <c r="O4" t="n">
         <v>16.5</v>
       </c>
       <c r="P4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.747</v>
+        <v>0.749</v>
       </c>
       <c r="R4" t="n">
         <v>10.2</v>
       </c>
       <c r="S4" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="V4" t="n">
         <v>14.3</v>
@@ -1085,7 +1152,7 @@
         <v>6.2</v>
       </c>
       <c r="X4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y4" t="n">
         <v>5.8</v>
@@ -1094,16 +1161,16 @@
         <v>19.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-13.3</v>
+        <v>-13.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1139,7 +1206,7 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
         <v>19</v>
@@ -1154,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="AU4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV4" t="n">
         <v>12</v>
@@ -1163,10 +1230,10 @@
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ4" t="n">
         <v>11</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
         <v>46</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.754</v>
+        <v>0.767</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
         <v>82.90000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L5" t="n">
         <v>6.4</v>
@@ -1237,7 +1304,7 @@
         <v>16.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O5" t="n">
         <v>15.5</v>
@@ -1270,22 +1337,22 @@
         <v>6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="AA5" t="n">
         <v>18</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL5" t="n">
         <v>17</v>
@@ -1315,13 +1382,13 @@
         <v>19</v>
       </c>
       <c r="AN5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ5" t="n">
         <v>27</v>
@@ -1348,7 +1415,7 @@
         <v>3</v>
       </c>
       <c r="AY5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE6" t="n">
         <v>26</v>
@@ -1482,7 +1549,7 @@
         <v>8</v>
       </c>
       <c r="AI6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ6" t="n">
         <v>17</v>
@@ -1497,7 +1564,7 @@
         <v>17</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>9</v>
@@ -1512,13 +1579,13 @@
         <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV6" t="n">
         <v>26</v>
@@ -1539,7 +1606,7 @@
         <v>6</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC6" t="n">
         <v>27</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -1571,52 +1638,52 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>34</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0.443</v>
       </c>
       <c r="L7" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M7" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
       <c r="O7" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="P7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.762</v>
+        <v>0.759</v>
       </c>
       <c r="R7" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S7" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T7" t="n">
         <v>42.7</v>
@@ -1628,7 +1695,7 @@
         <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X7" t="n">
         <v>5.2</v>
@@ -1637,13 +1704,13 @@
         <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.4</v>
+        <v>18.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>95.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AC7" t="n">
         <v>1.2</v>
@@ -1655,22 +1722,22 @@
         <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI7" t="n">
         <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1679,31 +1746,31 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP7" t="n">
         <v>27</v>
       </c>
-      <c r="AP7" t="n">
-        <v>26</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
         <v>27</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>14</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1715,7 +1782,7 @@
         <v>2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
@@ -1777,13 +1844,13 @@
         <v>0.471</v>
       </c>
       <c r="L8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M8" t="n">
         <v>20.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.33</v>
+        <v>0.327</v>
       </c>
       <c r="O8" t="n">
         <v>19.9</v>
@@ -1792,10 +1859,10 @@
         <v>27.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.734</v>
+        <v>0.735</v>
       </c>
       <c r="R8" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S8" t="n">
         <v>32</v>
@@ -1813,10 +1880,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z8" t="n">
         <v>19.7</v>
@@ -1831,19 +1898,19 @@
         <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1852,7 +1919,7 @@
         <v>15</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1861,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>3</v>
@@ -1882,13 +1949,13 @@
         <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
         <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>15</v>
@@ -1897,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>22</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
         <v>9</v>
@@ -2031,7 +2098,7 @@
         <v>25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK9" t="n">
         <v>24</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>14</v>
@@ -2073,7 +2140,7 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY9" t="n">
         <v>21</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2117,28 +2184,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E10" t="n">
         <v>22</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.367</v>
+        <v>0.373</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J10" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L10" t="n">
         <v>8.199999999999999</v>
@@ -2147,25 +2214,25 @@
         <v>21</v>
       </c>
       <c r="N10" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O10" t="n">
         <v>14.8</v>
       </c>
       <c r="P10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.776</v>
+        <v>0.774</v>
       </c>
       <c r="R10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T10" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="U10" t="n">
         <v>22.4</v>
@@ -2183,19 +2250,19 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AA10" t="n">
         <v>16.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
         <v>22</v>
@@ -2210,13 +2277,13 @@
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -2234,7 +2301,7 @@
         <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
         <v>29</v>
@@ -2243,13 +2310,13 @@
         <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
         <v>10</v>
@@ -2267,7 +2334,7 @@
         <v>29</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E11" t="n">
         <v>32</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="H11" t="n">
         <v>48.7</v>
@@ -2317,7 +2384,7 @@
         <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K11" t="n">
         <v>0.45</v>
@@ -2326,10 +2393,10 @@
         <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O11" t="n">
         <v>15.8</v>
@@ -2347,7 +2414,7 @@
         <v>30.5</v>
       </c>
       <c r="T11" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U11" t="n">
         <v>21.2</v>
@@ -2356,10 +2423,10 @@
         <v>14.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y11" t="n">
         <v>5.2</v>
@@ -2371,13 +2438,13 @@
         <v>18.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>98.3</v>
+        <v>98.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2389,10 +2456,10 @@
         <v>14</v>
       </c>
       <c r="AH11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI11" t="n">
         <v>5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>6</v>
       </c>
       <c r="AJ11" t="n">
         <v>3</v>
@@ -2404,16 +2471,16 @@
         <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO11" t="n">
         <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ11" t="n">
         <v>3</v>
@@ -2437,10 +2504,10 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
         <v>22</v>
@@ -2449,10 +2516,10 @@
         <v>24</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>0.639</v>
+        <v>0.633</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,46 +2566,46 @@
         <v>35.4</v>
       </c>
       <c r="J12" t="n">
-        <v>80.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.439</v>
       </c>
       <c r="L12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M12" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="O12" t="n">
         <v>20.5</v>
       </c>
       <c r="P12" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R12" t="n">
         <v>12.3</v>
       </c>
       <c r="S12" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T12" t="n">
-        <v>43.7</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="V12" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X12" t="n">
         <v>5.5</v>
@@ -2547,37 +2614,37 @@
         <v>5.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA12" t="n">
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2589,7 +2656,7 @@
         <v>22</v>
       </c>
       <c r="AN12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,22 +2668,22 @@
         <v>4</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>8</v>
@@ -2631,7 +2698,7 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC12" t="n">
         <v>6</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
         <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>0.623</v>
+        <v>0.617</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2684,7 +2751,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L13" t="n">
         <v>7.7</v>
@@ -2693,19 +2760,19 @@
         <v>21.8</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P13" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q13" t="n">
         <v>0.679</v>
       </c>
       <c r="R13" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S13" t="n">
         <v>29.6</v>
@@ -2723,7 +2790,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y13" t="n">
         <v>4.6</v>
@@ -2735,13 +2802,13 @@
         <v>21.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2753,7 +2820,7 @@
         <v>7</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI13" t="n">
         <v>13</v>
@@ -2774,7 +2841,7 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -2783,7 +2850,7 @@
         <v>29</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
         <v>25</v>
@@ -2798,13 +2865,13 @@
         <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
         <v>24</v>
@@ -2813,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>8</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -2935,7 +3002,7 @@
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI14" t="n">
         <v>14</v>
@@ -2974,7 +3041,7 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>22</v>
@@ -2995,7 +3062,7 @@
         <v>9</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC14" t="n">
         <v>11</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3105,16 +3172,16 @@
         <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
         <v>8</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH15" t="n">
         <v>15</v>
@@ -3123,7 +3190,7 @@
         <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
         <v>17</v>
@@ -3135,31 +3202,31 @@
         <v>28</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
         <v>10</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3174,13 +3241,13 @@
         <v>18</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>20</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F16" t="n">
         <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.717</v>
+        <v>0.712</v>
       </c>
       <c r="H16" t="n">
         <v>48.7</v>
@@ -3227,7 +3294,7 @@
         <v>37.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K16" t="n">
         <v>0.474</v>
@@ -3242,22 +3309,22 @@
         <v>0.363</v>
       </c>
       <c r="O16" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S16" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T16" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U16" t="n">
         <v>20.4</v>
@@ -3266,7 +3333,7 @@
         <v>14.8</v>
       </c>
       <c r="W16" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X16" t="n">
         <v>5.4</v>
@@ -3287,22 +3354,22 @@
         <v>6.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
       </c>
       <c r="AF16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>4</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
         <v>24</v>
@@ -3311,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="AL16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM16" t="n">
         <v>23</v>
@@ -3326,19 +3393,19 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
       </c>
       <c r="AS16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV16" t="n">
         <v>17</v>
@@ -3350,13 +3417,13 @@
         <v>9</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>0.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
         <v>19</v>
@@ -3508,7 +3575,7 @@
         <v>24</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR17" t="n">
         <v>6</v>
@@ -3523,16 +3590,16 @@
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3544,7 +3611,7 @@
         <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3573,37 +3640,37 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.403</v>
+        <v>0.41</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J18" t="n">
         <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L18" t="n">
         <v>7.2</v>
       </c>
       <c r="M18" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O18" t="n">
         <v>19.4</v>
@@ -3612,7 +3679,7 @@
         <v>25.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
@@ -3624,31 +3691,31 @@
         <v>43.8</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W18" t="n">
         <v>6.8</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z18" t="n">
         <v>18.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.9</v>
+        <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1</v>
@@ -3663,7 +3730,7 @@
         <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>20</v>
@@ -3690,19 +3757,19 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
@@ -3711,19 +3778,19 @@
         <v>25</v>
       </c>
       <c r="AX18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC18" t="n">
         <v>21</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3755,46 +3822,46 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E19" t="n">
         <v>22</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>34.4</v>
+        <v>34.3</v>
       </c>
       <c r="J19" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.426</v>
+        <v>0.425</v>
       </c>
       <c r="L19" t="n">
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
         <v>12.1</v>
@@ -3803,7 +3870,7 @@
         <v>28.3</v>
       </c>
       <c r="T19" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U19" t="n">
         <v>20.1</v>
@@ -3815,7 +3882,7 @@
         <v>7.6</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
         <v>5</v>
@@ -3839,7 +3906,7 @@
         <v>22</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
         <v>24</v>
@@ -3848,10 +3915,10 @@
         <v>27</v>
       </c>
       <c r="AI19" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
@@ -3863,16 +3930,16 @@
         <v>3</v>
       </c>
       <c r="AN19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR19" t="n">
         <v>10</v>
@@ -3884,16 +3951,16 @@
         <v>26</v>
       </c>
       <c r="AU19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
         <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY19" t="n">
         <v>16</v>
@@ -3902,10 +3969,10 @@
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -3937,28 +4004,28 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F20" t="n">
         <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>0.311</v>
+        <v>0.3</v>
       </c>
       <c r="H20" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>35.2</v>
       </c>
       <c r="J20" t="n">
         <v>77.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L20" t="n">
         <v>4</v>
@@ -3967,55 +4034,55 @@
         <v>11.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.338</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P20" t="n">
         <v>20.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R20" t="n">
         <v>11</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="V20" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>89.5</v>
+        <v>89.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4033,22 +4100,22 @@
         <v>24</v>
       </c>
       <c r="AJ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL20" t="n">
         <v>29</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>30</v>
       </c>
       <c r="AM20" t="n">
         <v>30</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AO20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
         <v>25</v>
@@ -4057,10 +4124,10 @@
         <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AS20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4072,13 +4139,13 @@
         <v>25</v>
       </c>
       <c r="AW20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX20" t="n">
         <v>21</v>
       </c>
       <c r="AY20" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ20" t="n">
         <v>19</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -4197,13 +4264,13 @@
         <v>2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG21" t="n">
         <v>16</v>
@@ -4230,7 +4297,7 @@
         <v>26</v>
       </c>
       <c r="AO21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP21" t="n">
         <v>4</v>
@@ -4242,7 +4309,7 @@
         <v>15</v>
       </c>
       <c r="AS21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
         <v>14</v>
@@ -4251,13 +4318,13 @@
         <v>23</v>
       </c>
       <c r="AV21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY21" t="n">
         <v>18</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
         <v>7</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -4301,67 +4368,67 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E22" t="n">
         <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
-        <v>0.721</v>
+        <v>0.733</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J22" t="n">
-        <v>78.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.474</v>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
         <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>0.356</v>
+        <v>0.359</v>
       </c>
       <c r="O22" t="n">
         <v>21.1</v>
       </c>
       <c r="P22" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.799</v>
+        <v>0.803</v>
       </c>
       <c r="R22" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S22" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T22" t="n">
         <v>43.6</v>
       </c>
       <c r="U22" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="V22" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W22" t="n">
         <v>7.6</v>
       </c>
       <c r="X22" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="Y22" t="n">
         <v>4.7</v>
@@ -4373,31 +4440,31 @@
         <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>102.7</v>
+        <v>103.1</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
       </c>
       <c r="AF22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>2</v>
@@ -4409,7 +4476,7 @@
         <v>12</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4424,16 +4491,16 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
         <v>17</v>
@@ -4448,7 +4515,7 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -4483,58 +4550,58 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F23" t="n">
         <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>0.59</v>
+        <v>0.583</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>34.5</v>
+        <v>34.3</v>
       </c>
       <c r="J23" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L23" t="n">
         <v>10.2</v>
       </c>
       <c r="M23" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="O23" t="n">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="P23" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.658</v>
+        <v>0.656</v>
       </c>
       <c r="R23" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
         <v>31.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
         <v>15</v>
@@ -4549,40 +4616,40 @@
         <v>4</v>
       </c>
       <c r="Z23" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF23" t="n">
         <v>8</v>
       </c>
       <c r="AG23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AJ23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4591,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4612,10 +4679,10 @@
         <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
         <v>26</v>
@@ -4630,7 +4697,7 @@
         <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>31</v>
       </c>
       <c r="F24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.517</v>
+        <v>0.525</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J24" t="n">
         <v>83.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L24" t="n">
         <v>5.2</v>
@@ -4695,10 +4762,10 @@
         <v>14.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="P24" t="n">
         <v>17.9</v>
@@ -4707,16 +4774,16 @@
         <v>0.741</v>
       </c>
       <c r="R24" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S24" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>43.2</v>
       </c>
       <c r="U24" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V24" t="n">
         <v>11.1</v>
@@ -4728,37 +4795,37 @@
         <v>5.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AA24" t="n">
         <v>16.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF24" t="n">
         <v>14</v>
       </c>
       <c r="AG24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ24" t="n">
         <v>5</v>
@@ -4767,13 +4834,13 @@
         <v>15</v>
       </c>
       <c r="AL24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4782,19 +4849,19 @@
         <v>30</v>
       </c>
       <c r="AQ24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
         <v>5</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" t="n">
         <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.525</v>
+        <v>0.517</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J25" t="n">
         <v>82.2</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O25" t="n">
         <v>16.1</v>
       </c>
       <c r="P25" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.758</v>
       </c>
       <c r="R25" t="n">
         <v>10.8</v>
@@ -4898,7 +4965,7 @@
         <v>41.6</v>
       </c>
       <c r="U25" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V25" t="n">
         <v>14</v>
@@ -4916,46 +4983,46 @@
         <v>18.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>98.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>30</v>
       </c>
       <c r="AI25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO25" t="n">
         <v>18</v>
@@ -4964,7 +5031,7 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -4973,13 +5040,13 @@
         <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4988,16 +5055,16 @@
         <v>5</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5029,25 +5096,25 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G26" t="n">
-        <v>0.452</v>
+        <v>0.459</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>0.446</v>
@@ -5068,19 +5135,19 @@
         <v>21.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.795</v>
+        <v>0.796</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
         <v>14.1</v>
@@ -5101,10 +5168,10 @@
         <v>19.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -5137,22 +5204,22 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO26" t="n">
         <v>13</v>
       </c>
-      <c r="AO26" t="n">
-        <v>12</v>
-      </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5170,19 +5237,19 @@
         <v>16</v>
       </c>
       <c r="AY26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
       </c>
       <c r="BA26" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB26" t="n">
         <v>13</v>
       </c>
-      <c r="BB26" t="n">
-        <v>12</v>
-      </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-6.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,10 +5368,10 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
         <v>1</v>
@@ -5328,16 +5395,16 @@
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU27" t="n">
         <v>26</v>
@@ -5349,7 +5416,7 @@
         <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.729</v>
+        <v>0.724</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5411,40 +5478,40 @@
         <v>38.9</v>
       </c>
       <c r="J28" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M28" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="P28" t="n">
         <v>21.3</v>
       </c>
-      <c r="N28" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="O28" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="P28" t="n">
-        <v>21.6</v>
-      </c>
       <c r="Q28" t="n">
-        <v>0.742</v>
+        <v>0.739</v>
       </c>
       <c r="R28" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S28" t="n">
         <v>32.4</v>
       </c>
       <c r="T28" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U28" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V28" t="n">
         <v>13.5</v>
@@ -5459,19 +5526,19 @@
         <v>5</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>102.1</v>
+        <v>101.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5480,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH28" t="n">
         <v>14</v>
@@ -5492,7 +5559,7 @@
         <v>8</v>
       </c>
       <c r="AK28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="n">
         <v>2</v>
@@ -5504,25 +5571,25 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS28" t="n">
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
         <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5602,22 +5669,22 @@
         <v>5.6</v>
       </c>
       <c r="M29" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O29" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P29" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R29" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S29" t="n">
         <v>31.2</v>
@@ -5641,16 +5708,16 @@
         <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>91.2</v>
+        <v>91.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.5</v>
+        <v>-3.2</v>
       </c>
       <c r="AD29" t="n">
         <v>1</v>
@@ -5659,7 +5726,7 @@
         <v>22</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
         <v>24</v>
@@ -5668,22 +5735,22 @@
         <v>12</v>
       </c>
       <c r="AI29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ29" t="n">
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
         <v>15</v>
@@ -5692,13 +5759,13 @@
         <v>17</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>22</v>
       </c>
       <c r="AS29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>19</v>
@@ -5707,13 +5774,13 @@
         <v>15</v>
       </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -5722,7 +5789,7 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB29" t="n">
         <v>27</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5757,61 +5824,61 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
         <v>30</v>
       </c>
       <c r="G30" t="n">
-        <v>0.516</v>
+        <v>0.508</v>
       </c>
       <c r="H30" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.456</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M30" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="O30" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P30" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R30" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="S30" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T30" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V30" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W30" t="n">
         <v>8.199999999999999</v>
@@ -5823,13 +5890,13 @@
         <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>99.2</v>
+        <v>98.8</v>
       </c>
       <c r="AC30" t="n">
         <v>-0.1</v>
@@ -5838,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5859,7 +5926,7 @@
         <v>9</v>
       </c>
       <c r="AL30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM30" t="n">
         <v>29</v>
@@ -5868,7 +5935,7 @@
         <v>29</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5880,31 +5947,31 @@
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ30" t="n">
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
         <v>46</v>
       </c>
       <c r="G31" t="n">
-        <v>0.246</v>
+        <v>0.233</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5957,28 +6024,28 @@
         <v>36.1</v>
       </c>
       <c r="J31" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="M31" t="n">
         <v>16.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.319</v>
+        <v>0.321</v>
       </c>
       <c r="O31" t="n">
         <v>15.6</v>
       </c>
       <c r="P31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.732</v>
+        <v>0.731</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
@@ -5996,28 +6063,28 @@
         <v>15.3</v>
       </c>
       <c r="W31" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z31" t="n">
         <v>21.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.6</v>
+        <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
         <v>19</v>
@@ -6041,19 +6108,19 @@
         <v>25</v>
       </c>
       <c r="AL31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN31" t="n">
         <v>27</v>
       </c>
       <c r="AO31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
@@ -6062,10 +6129,10 @@
         <v>13</v>
       </c>
       <c r="AS31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6074,22 +6141,22 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-16-2011-12</t>
+          <t>2012-04-16</t>
         </is>
       </c>
     </row>
